--- a/public/sales_report/transactions_report.xlsx
+++ b/public/sales_report/transactions_report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>ID Transaction</t>
   </si>
@@ -38,51 +38,6 @@
   </si>
   <si>
     <t>Created At</t>
-  </si>
-  <si>
-    <t>24a0cd7d-d335-43c7-8dcb-fa1a3e7ca763</t>
-  </si>
-  <si>
-    <t>adinda</t>
-  </si>
-  <si>
-    <t>10000.00</t>
-  </si>
-  <si>
-    <t>0.00</t>
-  </si>
-  <si>
-    <t>paid</t>
-  </si>
-  <si>
-    <t>qris</t>
-  </si>
-  <si>
-    <t>11/30/2024, 8:00:00 AM</t>
-  </si>
-  <si>
-    <t>64f5bca3-d265-418c-9bf3-364e36492d47</t>
-  </si>
-  <si>
-    <t>50000.00</t>
-  </si>
-  <si>
-    <t>12/1/2024, 3:41:01 PM</t>
-  </si>
-  <si>
-    <t>be9ae2d3-7a73-489e-b775-7089791db15b</t>
-  </si>
-  <si>
-    <t>20000.00</t>
-  </si>
-  <si>
-    <t>12/10/2024, 3:41:01 PM</t>
-  </si>
-  <si>
-    <t>8c1ae951-0af1-42de-8c35-adb7fd3f6e98</t>
-  </si>
-  <si>
-    <t>12/10/2024, 3:41:14 PM</t>
   </si>
 </sst>
 </file>
@@ -459,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -500,122 +455,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
